--- a/Result/profitability/2913.xlsx
+++ b/Result/profitability/2913.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.03625</v>
+        <v>-0.0375</v>
       </c>
       <c r="N2" t="n">
-        <v>35.06875</v>
+        <v>34.84875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.13</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.04625</v>
+        <v>-0.0475</v>
       </c>
       <c r="N3" t="n">
-        <v>31.2075</v>
+        <v>30.40125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -901,10 +901,10 @@
         <v>0.17</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.01875</v>
+        <v>-0.02125</v>
       </c>
       <c r="N4" t="n">
-        <v>26.71875</v>
+        <v>26.15875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1020,10 +1020,10 @@
         <v>-0.03</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0175</v>
+        <v>-0.02</v>
       </c>
       <c r="N5" t="n">
-        <v>22.19875</v>
+        <v>21.7075</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1139,10 +1139,10 @@
         <v>0.01</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.01125</v>
+        <v>-0.015</v>
       </c>
       <c r="N6" t="n">
-        <v>18.6675</v>
+        <v>18.44875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1268,10 +1268,10 @@
         <v>-0.02</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.009999999999999998</v>
+        <v>-0.0125</v>
       </c>
       <c r="N7" t="n">
-        <v>14.825</v>
+        <v>14.0525</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1395,10 +1395,10 @@
         <v>0.04</v>
       </c>
       <c r="M8" t="n">
-        <v>8.673617379884035e-19</v>
+        <v>-0.002499999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>10.785</v>
+        <v>10.36875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9842,6 +9842,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2913</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>99</v>
+      </c>
+      <c r="D75" t="n">
+        <v>65</v>
+      </c>
+      <c r="E75" t="n">
+        <v>34</v>
+      </c>
+      <c r="F75" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-15</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-15.25%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-32</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-47</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-47</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.04375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>38.005</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.329999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.08797886393659171</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.93</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1022106631989597</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
